--- a/uploads/Students_Directory_ALL_2026-09-27.xlsx
+++ b/uploads/Students_Directory_ALL_2026-09-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0e9a1f59ec589879/Desktop/plc/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2BF9D73ED410EB058E7DF3D70FEF16A979FA8D8A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{468919BB-ED3C-401B-8DDC-976C8C395FC2}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_2BF9D73ED410EB058E7DF3D70FEF16A979FA8D8A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A495C81A-6FC3-4617-B90D-236885EFAA42}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="205">
   <si>
     <t>id</t>
   </si>
@@ -88,9 +88,6 @@
     <t>Ananya Iyer</t>
   </si>
   <si>
-    <t>AIDS</t>
-  </si>
-  <si>
     <t>NVIDIA</t>
   </si>
   <si>
@@ -638,6 +635,9 @@
   </si>
   <si>
     <t>DS</t>
+  </si>
+  <si>
+    <t>AIML</t>
   </si>
 </sst>
 </file>
@@ -690,6 +690,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1077,7 +1081,7 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D3">
         <v>9.7200000000000006</v>
@@ -1101,7 +1105,7 @@
         <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
         <v>18</v>
@@ -1109,10 +1113,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -1139,7 +1143,7 @@
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L4" t="s">
         <v>18</v>
@@ -1147,13 +1151,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
       </c>
       <c r="D5">
         <v>9.3000000000000007</v>
@@ -1177,7 +1181,7 @@
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L5" t="s">
         <v>18</v>
@@ -1185,13 +1189,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
       </c>
       <c r="D6">
         <v>8.92</v>
@@ -1215,7 +1219,7 @@
         <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
         <v>18</v>
@@ -1223,10 +1227,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
         <v>34</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -1253,7 +1257,7 @@
         <v>16</v>
       </c>
       <c r="K7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L7" t="s">
         <v>18</v>
@@ -1261,10 +1265,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
         <v>37</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -1285,13 +1289,13 @@
         <v>666</v>
       </c>
       <c r="I8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" t="s">
         <v>39</v>
       </c>
-      <c r="J8" t="s">
-        <v>40</v>
-      </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L8" t="s">
         <v>18</v>
@@ -1299,13 +1303,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
         <v>42</v>
       </c>
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>8.6999999999999993</v>
@@ -1323,13 +1327,13 @@
         <v>700</v>
       </c>
       <c r="I9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L9" t="s">
         <v>18</v>
@@ -1337,13 +1341,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
         <v>45</v>
       </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D10">
         <v>8.65</v>
@@ -1361,13 +1365,13 @@
         <v>772</v>
       </c>
       <c r="I10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L10" t="s">
         <v>18</v>
@@ -1375,13 +1379,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
         <v>48</v>
       </c>
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11">
         <v>8.4</v>
@@ -1399,13 +1403,13 @@
         <v>664</v>
       </c>
       <c r="I11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11" t="s">
         <v>39</v>
       </c>
-      <c r="J11" t="s">
-        <v>40</v>
-      </c>
       <c r="K11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L11" t="s">
         <v>18</v>
@@ -1413,13 +1417,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
         <v>50</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>51</v>
-      </c>
-      <c r="C12" t="s">
-        <v>52</v>
       </c>
       <c r="D12">
         <v>9.26</v>
@@ -1437,10 +1441,10 @@
         <v>697</v>
       </c>
       <c r="I12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K12" t="s">
         <v>17</v>
@@ -1451,13 +1455,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
         <v>53</v>
       </c>
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13">
         <v>6.83</v>
@@ -1475,13 +1479,13 @@
         <v>769</v>
       </c>
       <c r="I13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L13" t="s">
         <v>18</v>
@@ -1489,13 +1493,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
         <v>57</v>
       </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14">
         <v>7.46</v>
@@ -1513,13 +1517,13 @@
         <v>661</v>
       </c>
       <c r="I14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L14" t="s">
         <v>18</v>
@@ -1527,13 +1531,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
         <v>59</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>61</v>
       </c>
       <c r="D15">
         <v>8.09</v>
@@ -1551,13 +1555,13 @@
         <v>694</v>
       </c>
       <c r="I15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L15" t="s">
         <v>18</v>
@@ -1565,13 +1569,13 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s">
         <v>62</v>
       </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16">
         <v>8.7200000000000006</v>
@@ -1595,7 +1599,7 @@
         <v>16</v>
       </c>
       <c r="K16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L16" t="s">
         <v>18</v>
@@ -1603,13 +1607,13 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
         <v>65</v>
       </c>
-      <c r="B17" t="s">
-        <v>66</v>
-      </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D17">
         <v>9.35</v>
@@ -1627,13 +1631,13 @@
         <v>658</v>
       </c>
       <c r="I17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L17" t="s">
         <v>18</v>
@@ -1641,10 +1645,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
         <v>67</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
@@ -1665,13 +1669,13 @@
         <v>764</v>
       </c>
       <c r="I18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L18" t="s">
         <v>18</v>
@@ -1679,13 +1683,13 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" t="s">
         <v>69</v>
       </c>
-      <c r="B19" t="s">
-        <v>70</v>
-      </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19">
         <v>7.37</v>
@@ -1703,13 +1707,13 @@
         <v>617</v>
       </c>
       <c r="I19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L19" t="s">
         <v>18</v>
@@ -1717,13 +1721,13 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
         <v>71</v>
       </c>
-      <c r="B20" t="s">
-        <v>72</v>
-      </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>8</v>
@@ -1747,7 +1751,7 @@
         <v>16</v>
       </c>
       <c r="K20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L20" t="s">
         <v>18</v>
@@ -1755,13 +1759,13 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
         <v>73</v>
       </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D21">
         <v>8.6300000000000008</v>
@@ -1785,7 +1789,7 @@
         <v>16</v>
       </c>
       <c r="K21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L21" t="s">
         <v>18</v>
@@ -1793,13 +1797,13 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
         <v>75</v>
       </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D22">
         <v>9.26</v>
@@ -1817,13 +1821,13 @@
         <v>653</v>
       </c>
       <c r="I22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J22" t="s">
         <v>39</v>
       </c>
-      <c r="J22" t="s">
-        <v>40</v>
-      </c>
       <c r="K22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L22" t="s">
         <v>18</v>
@@ -1831,13 +1835,13 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" t="s">
         <v>77</v>
       </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D23">
         <v>6.65</v>
@@ -1855,13 +1859,13 @@
         <v>614</v>
       </c>
       <c r="I23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L23" t="s">
         <v>18</v>
@@ -1869,10 +1873,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
         <v>79</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -1899,7 +1903,7 @@
         <v>16</v>
       </c>
       <c r="K24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L24" t="s">
         <v>18</v>
@@ -1907,13 +1911,13 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
         <v>81</v>
       </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25">
         <v>7.91</v>
@@ -1931,13 +1935,13 @@
         <v>578</v>
       </c>
       <c r="I25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L25" t="s">
         <v>18</v>
@@ -1945,13 +1949,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" t="s">
         <v>83</v>
       </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D26">
         <v>8.5399999999999991</v>
@@ -1969,13 +1973,13 @@
         <v>612</v>
       </c>
       <c r="I26" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" t="s">
         <v>39</v>
       </c>
-      <c r="J26" t="s">
-        <v>40</v>
-      </c>
       <c r="K26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L26" t="s">
         <v>18</v>
@@ -1983,13 +1987,13 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" t="s">
         <v>85</v>
       </c>
-      <c r="B27" t="s">
-        <v>86</v>
-      </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D27">
         <v>9.17</v>
@@ -2013,7 +2017,7 @@
         <v>16</v>
       </c>
       <c r="K27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L27" t="s">
         <v>18</v>
@@ -2021,13 +2025,13 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D28">
         <v>8.81</v>
@@ -2045,13 +2049,13 @@
         <v>576</v>
       </c>
       <c r="I28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L28" t="s">
         <v>18</v>
@@ -2059,13 +2063,13 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" t="s">
         <v>89</v>
       </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D29">
         <v>7.19</v>
@@ -2083,13 +2087,13 @@
         <v>765</v>
       </c>
       <c r="I29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L29" t="s">
         <v>18</v>
@@ -2097,10 +2101,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -2121,13 +2125,13 @@
         <v>837</v>
       </c>
       <c r="I30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L30" t="s">
         <v>18</v>
@@ -2135,13 +2139,13 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
         <v>92</v>
       </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D31">
         <v>8.4499999999999993</v>
@@ -2159,13 +2163,13 @@
         <v>798</v>
       </c>
       <c r="I31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L31" t="s">
         <v>18</v>
@@ -2173,13 +2177,13 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" t="s">
         <v>94</v>
       </c>
-      <c r="B32" t="s">
-        <v>95</v>
-      </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D32">
         <v>9.08</v>
@@ -2203,7 +2207,7 @@
         <v>16</v>
       </c>
       <c r="K32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L32" t="s">
         <v>18</v>
@@ -2211,13 +2215,13 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" t="s">
         <v>96</v>
       </c>
-      <c r="B33" t="s">
-        <v>97</v>
-      </c>
       <c r="C33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33">
         <v>6.47</v>
@@ -2235,13 +2239,13 @@
         <v>842</v>
       </c>
       <c r="I33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L33" t="s">
         <v>18</v>
@@ -2249,13 +2253,13 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" t="s">
         <v>98</v>
       </c>
-      <c r="B34" t="s">
-        <v>99</v>
-      </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D34">
         <v>7.1</v>
@@ -2273,13 +2277,13 @@
         <v>875</v>
       </c>
       <c r="I34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L34" t="s">
         <v>18</v>
@@ -2287,13 +2291,13 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" t="s">
         <v>100</v>
       </c>
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D35">
         <v>7.73</v>
@@ -2311,13 +2315,13 @@
         <v>767</v>
       </c>
       <c r="I35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L35" t="s">
         <v>18</v>
@@ -2325,10 +2329,10 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" t="s">
         <v>102</v>
-      </c>
-      <c r="B36" t="s">
-        <v>103</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -2355,7 +2359,7 @@
         <v>16</v>
       </c>
       <c r="K36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L36" t="s">
         <v>18</v>
@@ -2363,13 +2367,13 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" t="s">
         <v>104</v>
       </c>
-      <c r="B37" t="s">
-        <v>105</v>
-      </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D37">
         <v>8.99</v>
@@ -2387,13 +2391,13 @@
         <v>873</v>
       </c>
       <c r="I37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L37" t="s">
         <v>18</v>
@@ -2401,13 +2405,13 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" t="s">
         <v>106</v>
       </c>
-      <c r="B38" t="s">
-        <v>107</v>
-      </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D38">
         <v>6.38</v>
@@ -2425,13 +2429,13 @@
         <v>765</v>
       </c>
       <c r="I38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L38" t="s">
         <v>18</v>
@@ -2439,13 +2443,13 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" t="s">
         <v>108</v>
       </c>
-      <c r="B39" t="s">
-        <v>109</v>
-      </c>
       <c r="C39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D39">
         <v>7.01</v>
@@ -2463,13 +2467,13 @@
         <v>837</v>
       </c>
       <c r="I39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L39" t="s">
         <v>18</v>
@@ -2477,13 +2481,13 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" t="s">
         <v>110</v>
       </c>
-      <c r="B40" t="s">
-        <v>111</v>
-      </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D40">
         <v>7.64</v>
@@ -2507,7 +2511,7 @@
         <v>16</v>
       </c>
       <c r="K40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L40" t="s">
         <v>18</v>
@@ -2515,13 +2519,13 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" t="s">
         <v>112</v>
       </c>
-      <c r="B41" t="s">
-        <v>113</v>
-      </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D41">
         <v>8.27</v>
@@ -2539,13 +2543,13 @@
         <v>690</v>
       </c>
       <c r="I41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L41" t="s">
         <v>18</v>
@@ -2553,10 +2557,10 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" t="s">
         <v>114</v>
-      </c>
-      <c r="B42" t="s">
-        <v>115</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
@@ -2583,7 +2587,7 @@
         <v>16</v>
       </c>
       <c r="K42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L42" t="s">
         <v>18</v>
@@ -2591,13 +2595,13 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" t="s">
         <v>116</v>
       </c>
-      <c r="B43" t="s">
-        <v>117</v>
-      </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D43">
         <v>6.29</v>
@@ -2615,13 +2619,13 @@
         <v>834</v>
       </c>
       <c r="I43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L43" t="s">
         <v>18</v>
@@ -2629,13 +2633,13 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D44">
         <v>8.4499999999999993</v>
@@ -2653,13 +2657,13 @@
         <v>796</v>
       </c>
       <c r="I44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L44" t="s">
         <v>18</v>
@@ -2667,13 +2671,13 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D45">
         <v>7.55</v>
@@ -2691,13 +2695,13 @@
         <v>688</v>
       </c>
       <c r="I45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L45" t="s">
         <v>18</v>
@@ -2705,13 +2709,13 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D46">
         <v>8.18</v>
@@ -2729,13 +2733,13 @@
         <v>760</v>
       </c>
       <c r="I46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L46" t="s">
         <v>18</v>
@@ -2743,13 +2747,13 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C47" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D47">
         <v>8.81</v>
@@ -2767,13 +2771,13 @@
         <v>793</v>
       </c>
       <c r="I47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L47" t="s">
         <v>18</v>
@@ -2781,10 +2785,10 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
@@ -2805,13 +2809,13 @@
         <v>685</v>
       </c>
       <c r="I48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L48" t="s">
         <v>18</v>
@@ -2819,13 +2823,13 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D49">
         <v>6.83</v>
@@ -2843,13 +2847,13 @@
         <v>757</v>
       </c>
       <c r="I49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L49" t="s">
         <v>18</v>
@@ -2857,13 +2861,13 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D50">
         <v>7.46</v>
@@ -2881,13 +2885,13 @@
         <v>790</v>
       </c>
       <c r="I50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L50" t="s">
         <v>18</v>
@@ -2895,13 +2899,13 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D51">
         <v>8.09</v>
@@ -2919,13 +2923,13 @@
         <v>682</v>
       </c>
       <c r="I51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L51" t="s">
         <v>18</v>
@@ -2933,13 +2937,13 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D52">
         <v>8.7200000000000006</v>
@@ -2963,7 +2967,7 @@
         <v>16</v>
       </c>
       <c r="K52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L52" t="s">
         <v>18</v>
@@ -2971,13 +2975,13 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D53">
         <v>9.35</v>
@@ -2995,13 +2999,13 @@
         <v>788</v>
       </c>
       <c r="I53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L53" t="s">
         <v>18</v>
@@ -3009,10 +3013,10 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
@@ -3033,13 +3037,13 @@
         <v>680</v>
       </c>
       <c r="I54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L54" t="s">
         <v>18</v>
@@ -3047,13 +3051,13 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D55">
         <v>7.37</v>
@@ -3071,13 +3075,13 @@
         <v>752</v>
       </c>
       <c r="I55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J55" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L55" t="s">
         <v>18</v>
@@ -3085,13 +3089,13 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D56">
         <v>8</v>
@@ -3115,7 +3119,7 @@
         <v>16</v>
       </c>
       <c r="K56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L56" t="s">
         <v>18</v>
@@ -3123,13 +3127,13 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57">
         <v>8.6300000000000008</v>
@@ -3153,7 +3157,7 @@
         <v>16</v>
       </c>
       <c r="K57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L57" t="s">
         <v>18</v>
@@ -3161,13 +3165,13 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B58" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D58">
         <v>9.26</v>
@@ -3185,13 +3189,13 @@
         <v>749</v>
       </c>
       <c r="I58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J58" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L58" t="s">
         <v>18</v>
@@ -3199,13 +3203,13 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C59" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D59">
         <v>6.65</v>
@@ -3223,13 +3227,13 @@
         <v>782</v>
       </c>
       <c r="I59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J59" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L59" t="s">
         <v>18</v>
@@ -3237,13 +3241,13 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D60">
         <v>8</v>
@@ -3267,7 +3271,7 @@
         <v>16</v>
       </c>
       <c r="K60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L60" t="s">
         <v>18</v>
@@ -3275,13 +3279,13 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D61">
         <v>7.91</v>
@@ -3299,13 +3303,13 @@
         <v>746</v>
       </c>
       <c r="I61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J61" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K61" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L61" t="s">
         <v>18</v>
@@ -3313,13 +3317,13 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B62" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D62">
         <v>8.5399999999999991</v>
@@ -3337,13 +3341,13 @@
         <v>708</v>
       </c>
       <c r="I62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J62" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L62" t="s">
         <v>18</v>
@@ -3351,13 +3355,13 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C63" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D63">
         <v>9.17</v>
@@ -3381,7 +3385,7 @@
         <v>16</v>
       </c>
       <c r="K63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L63" t="s">
         <v>18</v>
@@ -3389,13 +3393,13 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D64">
         <v>6.56</v>
@@ -3413,13 +3417,13 @@
         <v>672</v>
       </c>
       <c r="I64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J64" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L64" t="s">
         <v>18</v>
@@ -3427,13 +3431,13 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B65" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D65">
         <v>7.19</v>
@@ -3451,13 +3455,13 @@
         <v>744</v>
       </c>
       <c r="I65" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J65" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L65" t="s">
         <v>18</v>
@@ -3465,10 +3469,10 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -3489,13 +3493,13 @@
         <v>705</v>
       </c>
       <c r="I66" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J66" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K66" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L66" t="s">
         <v>18</v>
@@ -3503,13 +3507,13 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D67">
         <v>8.4499999999999993</v>
@@ -3527,13 +3531,13 @@
         <v>777</v>
       </c>
       <c r="I67" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J67" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K67" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L67" t="s">
         <v>18</v>
@@ -3541,13 +3545,13 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B68" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C68" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D68">
         <v>9.08</v>
@@ -3571,7 +3575,7 @@
         <v>16</v>
       </c>
       <c r="K68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L68" t="s">
         <v>18</v>
@@ -3579,13 +3583,13 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D69">
         <v>7.73</v>
@@ -3603,13 +3607,13 @@
         <v>702</v>
       </c>
       <c r="I69" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J69" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K69" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L69" t="s">
         <v>18</v>
@@ -3617,13 +3621,13 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B70" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C70" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D70">
         <v>7.1</v>
@@ -3641,13 +3645,13 @@
         <v>666</v>
       </c>
       <c r="I70" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J70" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L70" t="s">
         <v>18</v>
@@ -3655,13 +3659,13 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D71">
         <v>7.73</v>
@@ -3679,13 +3683,13 @@
         <v>700</v>
       </c>
       <c r="I71" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J71" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K71" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L71" t="s">
         <v>18</v>
@@ -3693,10 +3697,10 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B72" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
@@ -3723,7 +3727,7 @@
         <v>16</v>
       </c>
       <c r="K72" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L72" t="s">
         <v>18</v>
@@ -3731,13 +3735,13 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D73">
         <v>8.99</v>
@@ -3755,13 +3759,13 @@
         <v>664</v>
       </c>
       <c r="I73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J73" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K73" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L73" t="s">
         <v>18</v>
@@ -3769,13 +3773,13 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B74" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D74">
         <v>6.38</v>
@@ -3793,13 +3797,13 @@
         <v>697</v>
       </c>
       <c r="I74" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J74" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L74" t="s">
         <v>18</v>
@@ -3807,13 +3811,13 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C75" t="s">
-        <v>61</v>
+        <v>203</v>
       </c>
       <c r="D75">
         <v>7.01</v>
@@ -3831,13 +3835,13 @@
         <v>769</v>
       </c>
       <c r="I75" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J75" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K75" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L75" t="s">
         <v>18</v>
@@ -3845,13 +3849,13 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" t="s">
         <v>150</v>
       </c>
-      <c r="B76" t="s">
-        <v>151</v>
-      </c>
       <c r="C76" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D76">
         <v>7.64</v>
@@ -3875,7 +3879,7 @@
         <v>16</v>
       </c>
       <c r="K76" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L76" t="s">
         <v>18</v>
@@ -3883,13 +3887,13 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D77">
         <v>8.27</v>
@@ -3907,13 +3911,13 @@
         <v>694</v>
       </c>
       <c r="I77" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J77" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K77" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L77" t="s">
         <v>18</v>
@@ -3921,10 +3925,10 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B78" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -3951,7 +3955,7 @@
         <v>16</v>
       </c>
       <c r="K78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L78" t="s">
         <v>18</v>
@@ -3959,13 +3963,13 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D79">
         <v>6.29</v>
@@ -3983,13 +3987,13 @@
         <v>658</v>
       </c>
       <c r="I79" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J79" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K79" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L79" t="s">
         <v>18</v>
@@ -3997,13 +4001,13 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B80" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D80">
         <v>6.92</v>
@@ -4021,13 +4025,13 @@
         <v>764</v>
       </c>
       <c r="I80" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J80" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K80" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L80" t="s">
         <v>18</v>
@@ -4035,13 +4039,13 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C81" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D81">
         <v>7.55</v>
@@ -4059,13 +4063,13 @@
         <v>617</v>
       </c>
       <c r="I81" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J81" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K81" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L81" t="s">
         <v>18</v>
@@ -4073,13 +4077,13 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B82" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C82" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D82">
         <v>8.18</v>
@@ -4097,13 +4101,13 @@
         <v>689</v>
       </c>
       <c r="I82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J82" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K82" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L82" t="s">
         <v>18</v>
@@ -4111,13 +4115,13 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B83" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D83">
         <v>8.81</v>
@@ -4135,13 +4139,13 @@
         <v>581</v>
       </c>
       <c r="I83" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J83" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K83" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L83" t="s">
         <v>18</v>
@@ -4149,13 +4153,13 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B84" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D84">
         <v>7.37</v>
@@ -4173,13 +4177,13 @@
         <v>653</v>
       </c>
       <c r="I84" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K84" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L84" t="s">
         <v>18</v>
@@ -4187,13 +4191,13 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B85" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D85">
         <v>6.83</v>
@@ -4211,13 +4215,13 @@
         <v>614</v>
       </c>
       <c r="I85" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J85" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K85" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L85" t="s">
         <v>18</v>
@@ -4225,13 +4229,13 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B86" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C86" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D86">
         <v>7.46</v>
@@ -4249,13 +4253,13 @@
         <v>686</v>
       </c>
       <c r="I86" t="s">
+        <v>38</v>
+      </c>
+      <c r="J86" t="s">
         <v>39</v>
       </c>
-      <c r="J86" t="s">
-        <v>40</v>
-      </c>
       <c r="K86" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L86" t="s">
         <v>18</v>
@@ -4263,13 +4267,13 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B87" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C87" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D87">
         <v>8.09</v>
@@ -4287,13 +4291,13 @@
         <v>578</v>
       </c>
       <c r="I87" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J87" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K87" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L87" t="s">
         <v>18</v>
@@ -4301,13 +4305,13 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C88" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D88">
         <v>8.7200000000000006</v>
@@ -4331,7 +4335,7 @@
         <v>16</v>
       </c>
       <c r="K88" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L88" t="s">
         <v>18</v>
@@ -4339,13 +4343,13 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B89" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D89">
         <v>9.35</v>
@@ -4363,13 +4367,13 @@
         <v>684</v>
       </c>
       <c r="I89" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J89" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K89" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L89" t="s">
         <v>18</v>
@@ -4377,10 +4381,10 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B90" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -4401,13 +4405,13 @@
         <v>576</v>
       </c>
       <c r="I90" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J90" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K90" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L90" t="s">
         <v>18</v>
@@ -4415,13 +4419,13 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B91" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D91">
         <v>7.37</v>
@@ -4439,13 +4443,13 @@
         <v>681</v>
       </c>
       <c r="I91" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J91" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K91" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L91" t="s">
         <v>18</v>
@@ -4453,13 +4457,13 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>166</v>
+      </c>
+      <c r="B92" t="s">
         <v>167</v>
       </c>
-      <c r="B92" t="s">
-        <v>168</v>
-      </c>
       <c r="C92" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D92">
         <v>8</v>
@@ -4483,7 +4487,7 @@
         <v>16</v>
       </c>
       <c r="K92" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L92" t="s">
         <v>18</v>
@@ -4491,13 +4495,13 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C93" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D93">
         <v>8.6300000000000008</v>
@@ -4521,7 +4525,7 @@
         <v>16</v>
       </c>
       <c r="K93" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L93" t="s">
         <v>18</v>
@@ -4529,13 +4533,13 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B94" t="s">
+        <v>50</v>
+      </c>
+      <c r="C94" t="s">
         <v>51</v>
-      </c>
-      <c r="C94" t="s">
-        <v>52</v>
       </c>
       <c r="D94">
         <v>9.26</v>
@@ -4553,13 +4557,13 @@
         <v>604</v>
       </c>
       <c r="I94" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J94" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K94" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L94" t="s">
         <v>18</v>
@@ -4567,13 +4571,13 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C95" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D95">
         <v>6.65</v>
@@ -4591,13 +4595,13 @@
         <v>676</v>
       </c>
       <c r="I95" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J95" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K95" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L95" t="s">
         <v>18</v>
@@ -4605,10 +4609,10 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
@@ -4635,7 +4639,7 @@
         <v>16</v>
       </c>
       <c r="K96" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L96" t="s">
         <v>18</v>
@@ -4643,13 +4647,13 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C97" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D97">
         <v>7.91</v>
@@ -4667,13 +4671,13 @@
         <v>601</v>
       </c>
       <c r="I97" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J97" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K97" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L97" t="s">
         <v>18</v>
@@ -4681,13 +4685,13 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B98" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C98" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D98">
         <v>8.5399999999999991</v>
@@ -4705,13 +4709,13 @@
         <v>673</v>
       </c>
       <c r="I98" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J98" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L98" t="s">
         <v>18</v>
@@ -4719,13 +4723,13 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B99" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D99">
         <v>9.17</v>
@@ -4749,7 +4753,7 @@
         <v>16</v>
       </c>
       <c r="K99" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L99" t="s">
         <v>18</v>
@@ -4757,13 +4761,13 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B100" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C100" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D100">
         <v>6.83</v>
@@ -4781,13 +4785,13 @@
         <v>599</v>
       </c>
       <c r="I100" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J100" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K100" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L100" t="s">
         <v>18</v>
@@ -4795,13 +4799,13 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B101" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C101" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D101">
         <v>7.19</v>
@@ -4819,13 +4823,13 @@
         <v>563</v>
       </c>
       <c r="I101" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J101" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K101" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L101" t="s">
         <v>18</v>
@@ -4833,13 +4837,13 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="D102">
         <v>7.82</v>
@@ -4857,13 +4861,13 @@
         <v>689</v>
       </c>
       <c r="I102" t="s">
+        <v>38</v>
+      </c>
+      <c r="J102" t="s">
         <v>39</v>
       </c>
-      <c r="J102" t="s">
-        <v>40</v>
-      </c>
       <c r="K102" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L102" t="s">
         <v>18</v>
@@ -4871,13 +4875,13 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B103" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C103" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D103">
         <v>8.4499999999999993</v>
@@ -4895,13 +4899,13 @@
         <v>581</v>
       </c>
       <c r="I103" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J103" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K103" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L103" t="s">
         <v>18</v>
@@ -4909,13 +4913,13 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B104" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C104" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D104">
         <v>9.08</v>
@@ -4939,7 +4943,7 @@
         <v>16</v>
       </c>
       <c r="K104" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L104" t="s">
         <v>18</v>
@@ -4947,13 +4951,13 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B105" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C105" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D105">
         <v>6.47</v>
@@ -4971,13 +4975,13 @@
         <v>614</v>
       </c>
       <c r="I105" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J105" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K105" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L105" t="s">
         <v>18</v>
@@ -4985,13 +4989,13 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C106" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D106">
         <v>7.1</v>
@@ -5009,13 +5013,13 @@
         <v>686</v>
       </c>
       <c r="I106" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J106" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K106" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L106" t="s">
         <v>18</v>
@@ -5023,13 +5027,13 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B107" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C107" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D107">
         <v>7.73</v>
@@ -5047,13 +5051,13 @@
         <v>578</v>
       </c>
       <c r="I107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J107" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K107" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L107" t="s">
         <v>18</v>
@@ -5061,10 +5065,10 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B108" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C108" t="s">
         <v>14</v>
@@ -5091,7 +5095,7 @@
         <v>16</v>
       </c>
       <c r="K108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L108" t="s">
         <v>18</v>
@@ -5099,13 +5103,13 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B109" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C109" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D109">
         <v>8.99</v>
@@ -5123,13 +5127,13 @@
         <v>684</v>
       </c>
       <c r="I109" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J109" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K109" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L109" t="s">
         <v>18</v>
@@ -5137,13 +5141,13 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B110" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C110" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D110">
         <v>6.38</v>
@@ -5161,13 +5165,13 @@
         <v>576</v>
       </c>
       <c r="I110" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J110" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K110" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L110" t="s">
         <v>18</v>
@@ -5175,13 +5179,13 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B111" t="s">
+        <v>59</v>
+      </c>
+      <c r="C111" t="s">
         <v>60</v>
-      </c>
-      <c r="C111" t="s">
-        <v>61</v>
       </c>
       <c r="D111">
         <v>7.01</v>
@@ -5199,13 +5203,13 @@
         <v>664</v>
       </c>
       <c r="I111" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J111" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K111" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L111" t="s">
         <v>18</v>
@@ -5213,13 +5217,13 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B112" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C112" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D112">
         <v>7.64</v>
@@ -5243,7 +5247,7 @@
         <v>16</v>
       </c>
       <c r="K112" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L112" t="s">
         <v>18</v>
@@ -5251,13 +5255,13 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B113" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C113" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D113">
         <v>8.27</v>
@@ -5275,13 +5279,13 @@
         <v>769</v>
       </c>
       <c r="I113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J113" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K113" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L113" t="s">
         <v>18</v>
@@ -5289,10 +5293,10 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B114" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
@@ -5319,7 +5323,7 @@
         <v>16</v>
       </c>
       <c r="K114" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L114" t="s">
         <v>18</v>
@@ -5327,13 +5331,13 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B115" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C115" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D115">
         <v>6.29</v>
@@ -5351,13 +5355,13 @@
         <v>694</v>
       </c>
       <c r="I115" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J115" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K115" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L115" t="s">
         <v>18</v>
@@ -5365,10 +5369,10 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B116" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C116" t="s">
         <v>14</v>
@@ -5389,13 +5393,13 @@
         <v>766</v>
       </c>
       <c r="I116" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J116" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K116" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L116" t="s">
         <v>18</v>
@@ -5403,13 +5407,13 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B117" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C117" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D117">
         <v>7.55</v>
@@ -5427,13 +5431,13 @@
         <v>658</v>
       </c>
       <c r="I117" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J117" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K117" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L117" t="s">
         <v>18</v>
@@ -5441,13 +5445,13 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B118" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C118" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D118">
         <v>9.35</v>
@@ -5459,13 +5463,13 @@
         <v>835</v>
       </c>
       <c r="I118" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J118" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K118" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L118" t="s">
         <v>18</v>
@@ -5473,13 +5477,13 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B119" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C119" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="D119">
         <v>8.81</v>
@@ -5491,13 +5495,13 @@
         <v>927</v>
       </c>
       <c r="I119" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J119" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L119" t="s">
         <v>18</v>
@@ -5505,13 +5509,13 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B120" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C120" t="s">
-        <v>52</v>
+        <v>203</v>
       </c>
       <c r="D120">
         <v>8.7200000000000006</v>
@@ -5529,7 +5533,7 @@
         <v>16</v>
       </c>
       <c r="K120" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L120" t="s">
         <v>18</v>
@@ -5537,13 +5541,13 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B121" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C121" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D121">
         <v>8.18</v>
@@ -5555,13 +5559,13 @@
         <v>837</v>
       </c>
       <c r="I121" t="s">
+        <v>38</v>
+      </c>
+      <c r="J121" t="s">
         <v>39</v>
       </c>
-      <c r="J121" t="s">
-        <v>40</v>
-      </c>
       <c r="K121" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L121" t="s">
         <v>18</v>
@@ -5569,13 +5573,13 @@
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B122" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C122" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D122">
         <v>8.09</v>
@@ -5587,13 +5591,13 @@
         <v>834</v>
       </c>
       <c r="I122" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J122" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K122" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L122" t="s">
         <v>18</v>
@@ -5601,13 +5605,13 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B123" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C123" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D123">
         <v>7.46</v>
@@ -5619,13 +5623,13 @@
         <v>744</v>
       </c>
       <c r="I123" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J123" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K123" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L123" t="s">
         <v>18</v>
@@ -5633,13 +5637,13 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B124" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C124" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D124">
         <v>6.83</v>
@@ -5651,13 +5655,13 @@
         <v>653</v>
       </c>
       <c r="I124" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J124" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K124" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L124" t="s">
         <v>18</v>
@@ -5665,10 +5669,10 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B125" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
@@ -5683,13 +5687,13 @@
         <v>563</v>
       </c>
       <c r="I125" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J125" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K125" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L125" t="s">
         <v>18</v>
@@ -5697,13 +5701,13 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
+        <v>201</v>
+      </c>
+      <c r="B126" t="s">
         <v>202</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>203</v>
-      </c>
-      <c r="C126" t="s">
-        <v>204</v>
       </c>
       <c r="D126">
         <v>8.1999999999999993</v>
@@ -5715,13 +5719,13 @@
         <v>722</v>
       </c>
       <c r="I126" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J126" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K126" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L126" t="s">
         <v>18</v>
